--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SECCIÓN DEPORTIVA ALJARAQUE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SECCIÓN DEPORTIVA ALJARAQUE.xlsx
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>21.5264</v>
+        <v>12.5519</v>
       </c>
       <c r="E3" t="n">
-        <v>24.7564</v>
+        <v>17.6968</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2298</v>
+        <v>-5.1452</v>
       </c>
       <c r="G3" t="n">
         <v>8.6685</v>
@@ -688,13 +688,13 @@
         <v>50.9542</v>
       </c>
       <c r="S3" t="n">
-        <v>7.1446</v>
+        <v>-1.8305</v>
       </c>
       <c r="T3" t="n">
-        <v>5.343</v>
+        <v>-1.7166</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8014</v>
+        <v>-0.1139</v>
       </c>
       <c r="V3" t="n">
         <v>-4.8475</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>F. BENÍTEZ SIERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>14.4197</v>
+        <v>7.8755</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6683999999999998</v>
+        <v>7.8755</v>
       </c>
       <c r="F4" t="n">
-        <v>13.7515</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.000999999999999</v>
+        <v>7.8755</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.2112</v>
+        <v>2.8988</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2101</v>
+        <v>4.9767</v>
       </c>
       <c r="J4" t="n">
-        <v>4.356</v>
+        <v>7.8755</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6648999999999999</v>
+        <v>2.8988</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6911</v>
+        <v>4.9767</v>
       </c>
       <c r="M4" t="n">
-        <v>-8.3569</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.8761</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4807</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.8173</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.0053</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>14.823</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>9.765000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8592</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>6.9059</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8384</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.4588</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. BENÍTEZ SIERRA</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>7.8755</v>
+        <v>6.8328</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8755</v>
+        <v>-3.6837</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>10.5162</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8755</v>
+        <v>-4.000999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8988</v>
+        <v>-6.2112</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9767</v>
+        <v>2.2101</v>
       </c>
       <c r="J5" t="n">
-        <v>7.8755</v>
+        <v>4.356</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8988</v>
+        <v>0.6648999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>4.9767</v>
+        <v>3.6911</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-8.3569</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-6.8761</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.4807</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.8173</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-10.0053</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>14.823</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.1778</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1.4929</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.6707</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.8384</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.4588</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3796</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>É. PINA FURTADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.689199999999998</v>
+        <v>2.8544</v>
       </c>
       <c r="E6" t="n">
-        <v>9.992699999999999</v>
+        <v>2.8544</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.303700000000001</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-14.7077</v>
+        <v>2.8544</v>
       </c>
       <c r="H6" t="n">
-        <v>-11.1077</v>
+        <v>1.6104</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.599899999999999</v>
+        <v>1.2442</v>
       </c>
       <c r="J6" t="n">
-        <v>31.5911</v>
+        <v>2.8544</v>
       </c>
       <c r="K6" t="n">
-        <v>20.9876</v>
+        <v>1.6104</v>
       </c>
       <c r="L6" t="n">
-        <v>10.6035</v>
+        <v>1.2442</v>
       </c>
       <c r="M6" t="n">
-        <v>-46.2987</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-32.0956</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-14.2029</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>25.5696</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-31.4986</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>57.0683</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>13.475</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>8.969200000000001</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4.5061</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-19.648</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9312</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.5795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>É. PINA FURTADO</t>
+          <t>D. PAVON CRUZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,43 +952,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8544</v>
+        <v>0.1579</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8544</v>
+        <v>-0.0547</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.2126</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8544</v>
+        <v>0.1306</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6104</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2442</v>
+        <v>0.1306</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8544</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6104</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2442</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.0274</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.0547</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. PAVON CRUZ</t>
+          <t>E. PINA FURTADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1087</v>
+        <v>-4.1913</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0547</v>
+        <v>-5.043100000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1634</v>
+        <v>0.8521000000000005</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1306</v>
+        <v>-2.3047</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-4.3302</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1306</v>
+        <v>2.025600000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>9.4481</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4.2057</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.242500000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1306</v>
+        <v>-11.7528</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-8.536000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1306</v>
+        <v>-3.2168</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-7.4115</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-19.8256</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>12.4142</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0219</v>
+        <v>0.9292000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0547</v>
+        <v>-0.6436999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0328</v>
+        <v>1.5729</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.5957</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>5.9783</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.3825</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. PINA FURTADO</t>
+          <t>C. CORRALES GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3557</v>
+        <v>-5.3381</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.783299999999999</v>
+        <v>-7.9977</v>
       </c>
       <c r="F9" t="n">
-        <v>2.427699999999999</v>
+        <v>2.659800000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3047</v>
+        <v>-6.820600000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.3302</v>
+        <v>-4.0451</v>
       </c>
       <c r="I9" t="n">
-        <v>2.025600000000001</v>
+        <v>-2.7756</v>
       </c>
       <c r="J9" t="n">
-        <v>9.4481</v>
+        <v>-2.1159</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2057</v>
+        <v>0.8757</v>
       </c>
       <c r="L9" t="n">
-        <v>5.242500000000001</v>
+        <v>-2.9917</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.7528</v>
+        <v>-4.704800000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.536000000000001</v>
+        <v>-4.9207</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.2168</v>
+        <v>0.2160000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.4115</v>
+        <v>8.337899999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-19.8256</v>
+        <v>-4.6322</v>
       </c>
       <c r="R9" t="n">
-        <v>12.4142</v>
+        <v>12.9701</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7647</v>
+        <v>-3.1436</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.384</v>
+        <v>-1.2496</v>
       </c>
       <c r="U9" t="n">
-        <v>3.1486</v>
+        <v>-1.894</v>
       </c>
       <c r="V9" t="n">
-        <v>4.5957</v>
+        <v>-3.7116</v>
       </c>
       <c r="W9" t="n">
-        <v>5.9783</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3825</v>
+        <v>-3.7116</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. CORRALES GARCIA</t>
+          <t>D. MORILLO LEON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.96</v>
+        <v>-8.414400000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.499000000000001</v>
+        <v>-5.2289</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5389</v>
+        <v>-3.1857</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.820600000000001</v>
+        <v>-5.593500000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.0451</v>
+        <v>-3.8405</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7756</v>
+        <v>-1.7532</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1159</v>
+        <v>3.8303</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8757</v>
+        <v>1.9366</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9917</v>
+        <v>1.8938</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.704800000000001</v>
+        <v>-9.424099999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.9207</v>
+        <v>-5.7768</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2160000000000001</v>
+        <v>-3.6471</v>
       </c>
       <c r="P10" t="n">
-        <v>8.337899999999999</v>
+        <v>2.7792</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.6322</v>
+        <v>-7.5967</v>
       </c>
       <c r="R10" t="n">
-        <v>12.9701</v>
+        <v>10.3761</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.7654</v>
+        <v>-1.3206</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7509</v>
+        <v>-1.7768</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.0148</v>
+        <v>0.4564000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.7116</v>
+        <v>-4.2799</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.7116</v>
+        <v>-4.5943</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. KONE</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.4008</v>
+        <v>-9.5433</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5669</v>
+        <v>-2.8765</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8339</v>
+        <v>-6.6667</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.456300000000001</v>
+        <v>-14.7077</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.0281</v>
+        <v>-11.1077</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.4283</v>
+        <v>-3.599899999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4452</v>
+        <v>31.5911</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7930999999999999</v>
+        <v>20.9876</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.2382</v>
+        <v>10.6035</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.0111</v>
+        <v>-46.2987</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.8213</v>
+        <v>-32.0956</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.19</v>
+        <v>-14.2029</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4087</v>
+        <v>25.5696</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.9291</v>
+        <v>-31.4986</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5204</v>
+        <v>57.0683</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3525</v>
+        <v>-0.7568000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8642</v>
+        <v>-3.9001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4884</v>
+        <v>3.1432</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8884</v>
+        <v>-19.648</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9433</v>
+        <v>0.9312</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8317</v>
+        <v>-20.5795</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MORILLO LEON</t>
+          <t>S. KONE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.6754</v>
+        <v>-11.1725</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.3517</v>
+        <v>-7.730499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3237</v>
+        <v>-3.4419</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.593500000000001</v>
+        <v>-8.456300000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.8405</v>
+        <v>-3.0281</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7532</v>
+        <v>-5.4283</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8303</v>
+        <v>-3.4452</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9366</v>
+        <v>0.7930999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8938</v>
+        <v>-4.2382</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.424099999999999</v>
+        <v>-5.0111</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.7768</v>
+        <v>-3.8213</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.6471</v>
+        <v>-1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7792</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.5967</v>
+        <v>-5.9291</v>
       </c>
       <c r="R12" t="n">
-        <v>10.3761</v>
+        <v>3.5204</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5813</v>
+        <v>1.5809</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.8996</v>
+        <v>0.7004999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3181999999999999</v>
+        <v>0.8804000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.2799</v>
+        <v>-1.8884</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3144</v>
+        <v>0.9433</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.5943</v>
+        <v>-2.8317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.258</v>
+        <v>-20.8583</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0985</v>
+        <v>-19.4677</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.3566</v>
+        <v>-1.3907</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.251599999999999</v>
+        <v>-9.569600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.9014</v>
+        <v>-14.0208</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6498</v>
+        <v>4.451</v>
       </c>
       <c r="J13" t="n">
-        <v>12.136</v>
+        <v>-0.9602000000000005</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5928</v>
+        <v>-5.7864</v>
       </c>
       <c r="L13" t="n">
-        <v>4.542899999999999</v>
+        <v>4.8262</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.3876</v>
+        <v>-8.6096</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.4943</v>
+        <v>-8.2341</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.8933</v>
+        <v>-0.3753</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.1882</v>
+        <v>-4.261799999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-27.7929</v>
+        <v>-16.861</v>
       </c>
       <c r="R13" t="n">
-        <v>22.6049</v>
+        <v>12.5994</v>
       </c>
       <c r="S13" t="n">
-        <v>18.1028</v>
+        <v>-1.6164</v>
       </c>
       <c r="T13" t="n">
-        <v>13.6667</v>
+        <v>-1.9606</v>
       </c>
       <c r="U13" t="n">
-        <v>4.4362</v>
+        <v>0.3444</v>
       </c>
       <c r="V13" t="n">
-        <v>-24.9217</v>
+        <v>-5.4104</v>
       </c>
       <c r="W13" t="n">
-        <v>4.0888</v>
+        <v>0.3144</v>
       </c>
       <c r="X13" t="n">
-        <v>-29.0103</v>
+        <v>-5.7249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>I. PEREZ SAENZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.5368</v>
+        <v>-23.5215</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.4152</v>
+        <v>-13.3045</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1218</v>
+        <v>-10.2174</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.569600000000001</v>
+        <v>-10.3736</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.0208</v>
+        <v>-7.4192</v>
       </c>
       <c r="I14" t="n">
-        <v>4.451</v>
+        <v>-2.9546</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9602000000000005</v>
+        <v>4.5985</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.7864</v>
+        <v>3.438299999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>4.8262</v>
+        <v>1.1604</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.6096</v>
+        <v>-14.9725</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.2341</v>
+        <v>-10.8571</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3753</v>
+        <v>-4.115</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.261799999999999</v>
+        <v>-1.111699999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.861</v>
+        <v>-15.1935</v>
       </c>
       <c r="R14" t="n">
-        <v>12.5994</v>
+        <v>14.0817</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.295</v>
+        <v>-2.5337</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.9085</v>
+        <v>-3.0233</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3866</v>
+        <v>0.4897000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.4104</v>
+        <v>-9.5029</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3144</v>
+        <v>0.3138999999999998</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.7249</v>
+        <v>-9.816699999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. PEREZ SAENZ</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
-        <v>-25.6103</v>
+        <v>-26.2169</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.3931</v>
+        <v>-9.1173</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.2171</v>
+        <v>-17.0996</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.3736</v>
+        <v>-1.251599999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.4192</v>
+        <v>-2.9014</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.9546</v>
+        <v>1.6498</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5985</v>
+        <v>12.136</v>
       </c>
       <c r="K15" t="n">
-        <v>3.438299999999999</v>
+        <v>7.5928</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1604</v>
+        <v>4.542899999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-14.9725</v>
+        <v>-13.3876</v>
       </c>
       <c r="N15" t="n">
-        <v>-10.8571</v>
+        <v>-10.4943</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.115</v>
+        <v>-2.8933</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.111699999999999</v>
+        <v>-5.1882</v>
       </c>
       <c r="Q15" t="n">
-        <v>-15.1935</v>
+        <v>-27.7929</v>
       </c>
       <c r="R15" t="n">
-        <v>14.0817</v>
+        <v>22.6049</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.6221</v>
+        <v>5.1444</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.1121</v>
+        <v>2.451</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.51</v>
+        <v>2.693</v>
       </c>
       <c r="V15" t="n">
-        <v>-9.5029</v>
+        <v>-24.9217</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3138999999999998</v>
+        <v>4.0888</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.816699999999999</v>
+        <v>-29.0103</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>-37.6195</v>
+        <v>-31.4542</v>
       </c>
       <c r="E16" t="n">
-        <v>-23.9226</v>
+        <v>-18.0557</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.697</v>
+        <v>-13.3984</v>
       </c>
       <c r="G16" t="n">
         <v>-26.7486</v>
@@ -1702,13 +1702,13 @@
         <v>31.6841</v>
       </c>
       <c r="S16" t="n">
-        <v>-15.057</v>
+        <v>-8.891300000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-13.3029</v>
+        <v>-7.436</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.7537</v>
+        <v>-1.4554</v>
       </c>
       <c r="V16" t="n">
         <v>-7.3019</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-61.5924</v>
+        <v>-45.77370000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-44.7362</v>
+        <v>-34.3639</v>
       </c>
       <c r="F17" t="n">
-        <v>-16.8564</v>
+        <v>-11.4098</v>
       </c>
       <c r="G17" t="n">
         <v>-35.8565</v>
@@ -1780,13 +1780,13 @@
         <v>37.9836</v>
       </c>
       <c r="S17" t="n">
-        <v>-26.9945</v>
+        <v>-11.1763</v>
       </c>
       <c r="T17" t="n">
-        <v>-18.5904</v>
+        <v>-8.2188</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.4039</v>
+        <v>-2.9575</v>
       </c>
       <c r="V17" t="n">
         <v>-15.4173</v>
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-75.16249999999999</v>
+        <v>-61.1469</v>
       </c>
       <c r="E18" t="n">
-        <v>-52.8472</v>
+        <v>-43.1926</v>
       </c>
       <c r="F18" t="n">
-        <v>-22.3155</v>
+        <v>-17.9543</v>
       </c>
       <c r="G18" t="n">
         <v>-22.502</v>
@@ -1858,13 +1858,13 @@
         <v>37.9838</v>
       </c>
       <c r="S18" t="n">
-        <v>-25.0784</v>
+        <v>-11.0627</v>
       </c>
       <c r="T18" t="n">
-        <v>-18.6243</v>
+        <v>-8.9694</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.4542</v>
+        <v>-2.0932</v>
       </c>
       <c r="V18" t="n">
         <v>-4.977499999999998</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>A. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-76.8031</v>
+        <v>-66.8573</v>
       </c>
       <c r="E19" t="n">
-        <v>-41.2584</v>
+        <v>-61.8823</v>
       </c>
       <c r="F19" t="n">
-        <v>-35.5445</v>
+        <v>-4.975099999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-41.7521</v>
+        <v>-41.1512</v>
       </c>
       <c r="H19" t="n">
-        <v>-19.1833</v>
+        <v>-22.2051</v>
       </c>
       <c r="I19" t="n">
-        <v>-22.5691</v>
+        <v>-18.9461</v>
       </c>
       <c r="J19" t="n">
-        <v>-14.5281</v>
+        <v>-4.8849</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.381</v>
+        <v>3.6899</v>
       </c>
       <c r="L19" t="n">
-        <v>-9.147</v>
+        <v>-8.5746</v>
       </c>
       <c r="M19" t="n">
-        <v>-27.224</v>
+        <v>-36.266</v>
       </c>
       <c r="N19" t="n">
-        <v>-13.8019</v>
+        <v>-25.8949</v>
       </c>
       <c r="O19" t="n">
-        <v>-13.4219</v>
+        <v>-10.3715</v>
       </c>
       <c r="P19" t="n">
-        <v>8.893599999999999</v>
+        <v>-31.3137</v>
       </c>
       <c r="Q19" t="n">
-        <v>-19.0844</v>
+        <v>-83.5646</v>
       </c>
       <c r="R19" t="n">
-        <v>27.9783</v>
+        <v>52.25069999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-10.4639</v>
+        <v>-10.5729</v>
       </c>
       <c r="T19" t="n">
-        <v>-8.271599999999999</v>
+        <v>-10.5635</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.1921</v>
+        <v>-0.009299999999999906</v>
       </c>
       <c r="V19" t="n">
-        <v>-33.4807</v>
+        <v>16.1801</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6259</v>
+        <v>37.1308</v>
       </c>
       <c r="X19" t="n">
-        <v>-34.107</v>
+        <v>-20.9507</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LLAMAS JIMENEZ</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-77.35420000000001</v>
+        <v>-73.04689999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-69.41379999999999</v>
+        <v>-39.32</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.9402</v>
+        <v>-33.7272</v>
       </c>
       <c r="G20" t="n">
-        <v>-41.1512</v>
+        <v>-41.7521</v>
       </c>
       <c r="H20" t="n">
-        <v>-22.2051</v>
+        <v>-19.1833</v>
       </c>
       <c r="I20" t="n">
-        <v>-18.9461</v>
+        <v>-22.5691</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.8849</v>
+        <v>-14.5281</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6899</v>
+        <v>-5.381</v>
       </c>
       <c r="L20" t="n">
-        <v>-8.5746</v>
+        <v>-9.147</v>
       </c>
       <c r="M20" t="n">
-        <v>-36.266</v>
+        <v>-27.224</v>
       </c>
       <c r="N20" t="n">
-        <v>-25.8949</v>
+        <v>-13.8019</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.3715</v>
+        <v>-13.4219</v>
       </c>
       <c r="P20" t="n">
-        <v>-31.3137</v>
+        <v>8.893599999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-83.5646</v>
+        <v>-19.0844</v>
       </c>
       <c r="R20" t="n">
-        <v>52.25069999999999</v>
+        <v>27.9783</v>
       </c>
       <c r="S20" t="n">
-        <v>-21.0697</v>
+        <v>-6.7079</v>
       </c>
       <c r="T20" t="n">
-        <v>-18.0954</v>
+        <v>-6.3333</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.974499999999999</v>
+        <v>-0.3745999999999998</v>
       </c>
       <c r="V20" t="n">
-        <v>16.1801</v>
+        <v>-33.4807</v>
       </c>
       <c r="W20" t="n">
-        <v>37.1308</v>
+        <v>0.6259</v>
       </c>
       <c r="X20" t="n">
-        <v>-20.9507</v>
+        <v>-34.107</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-337.7542</v>
+        <v>-325.1622</v>
       </c>
       <c r="E21" t="n">
-        <v>-214.8956</v>
+        <v>-210.7918</v>
       </c>
       <c r="F21" t="n">
-        <v>-122.8587</v>
+        <v>-114.3713</v>
       </c>
       <c r="G21" t="n">
         <v>-179.4594</v>
@@ -2083,7 +2083,7 @@
         <v>-95.0817</v>
       </c>
       <c r="P21" t="n">
-        <v>14.8217</v>
+        <v>14.82169999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-384.4686</v>
@@ -2092,13 +2092,13 @@
         <v>399.2927999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-62.3446</v>
+        <v>-49.75300000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-58.2921</v>
+        <v>-54.1878</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.052200000000001</v>
+        <v>4.4349</v>
       </c>
       <c r="V21" t="n">
         <v>-110.7736</v>
